--- a/Projects.xlsx
+++ b/Projects.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Documents\Projet IA\Dashboard_CV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BBB638A-F136-4C07-81AC-13EEB8D95B00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43D7BA1D-F741-4904-9894-22BB88D27955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -864,10 +864,10 @@
         <v>63</v>
       </c>
       <c r="G1" t="s">
+        <v>101</v>
+      </c>
+      <c r="H1" t="s">
         <v>100</v>
-      </c>
-      <c r="H1" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">

--- a/Projects.xlsx
+++ b/Projects.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Documents\Projet IA\Dashboard_CV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43D7BA1D-F741-4904-9894-22BB88D27955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA6874A3-D551-433B-803B-23ACD9828A73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -864,10 +864,10 @@
         <v>63</v>
       </c>
       <c r="G1" t="s">
+        <v>100</v>
+      </c>
+      <c r="H1" t="s">
         <v>101</v>
-      </c>
-      <c r="H1" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">

--- a/Projects.xlsx
+++ b/Projects.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER\Documents\Projet IA\Dashboard_CV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA6874A3-D551-433B-803B-23ACD9828A73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FDCEE18-C00B-4A5A-B7F3-99CE45B1D0A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="147">
   <si>
     <t>Project_name</t>
   </si>
@@ -314,15 +314,6 @@
     <t>https://github.com/camillefagbedji69-cpu/typology_project</t>
   </si>
   <si>
-    <t>Water Quality Analysis &amp; Potability Prediction</t>
-  </si>
-  <si>
-    <t>Accuracy = 0.69 ; F1-Score (1) = 0,65</t>
-  </si>
-  <si>
-    <t>https://github.com/camillefagbedji69-cpu/water_quality_project</t>
-  </si>
-  <si>
     <t>Carbon Modeling via GWR</t>
   </si>
   <si>
@@ -353,9 +344,6 @@
     <t>Lat</t>
   </si>
   <si>
-    <t>India</t>
-  </si>
-  <si>
     <t>9.325281925178674</t>
   </si>
   <si>
@@ -468,12 +456,6 @@
   </si>
   <si>
     <t xml:space="preserve"> 2.645346475411279</t>
-  </si>
-  <si>
-    <t>22.63411744927812</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 79.60198909586336</t>
   </si>
   <si>
     <t>9.343738390014984</t>
@@ -832,7 +814,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="80" bestFit="1" customWidth="1"/>
@@ -864,10 +846,10 @@
         <v>63</v>
       </c>
       <c r="G1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -890,10 +872,10 @@
         <v>65</v>
       </c>
       <c r="G2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="H2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -916,10 +898,10 @@
         <v>75</v>
       </c>
       <c r="G3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="H3" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -942,10 +924,10 @@
         <v>74</v>
       </c>
       <c r="G4" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="H4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -968,18 +950,18 @@
         <v>76</v>
       </c>
       <c r="G5" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="H5" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="B6" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="C6" t="s">
         <v>28</v>
@@ -994,18 +976,18 @@
         <v>73</v>
       </c>
       <c r="G6" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="H6" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B7" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="C7" t="s">
         <v>28</v>
@@ -1020,10 +1002,10 @@
         <v>73</v>
       </c>
       <c r="G7" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="H7" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -1046,10 +1028,10 @@
         <v>70</v>
       </c>
       <c r="G8" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H8" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -1072,10 +1054,10 @@
         <v>69</v>
       </c>
       <c r="G9" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="H9" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -1098,10 +1080,10 @@
         <v>88</v>
       </c>
       <c r="G10" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H10" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -1124,10 +1106,10 @@
         <v>82</v>
       </c>
       <c r="G11" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="H11" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -1150,10 +1132,10 @@
         <v>67</v>
       </c>
       <c r="G12" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="H12" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -1176,10 +1158,10 @@
         <v>66</v>
       </c>
       <c r="G13" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="H13" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -1202,10 +1184,10 @@
         <v>68</v>
       </c>
       <c r="G14" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="H14" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -1228,10 +1210,10 @@
         <v>71</v>
       </c>
       <c r="G15" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="H15" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1254,10 +1236,10 @@
         <v>72</v>
       </c>
       <c r="G16" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="H16" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -1280,10 +1262,10 @@
         <v>87</v>
       </c>
       <c r="G17" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="H17" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -1306,10 +1288,10 @@
         <v>81</v>
       </c>
       <c r="G18" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="H18" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -1332,10 +1314,10 @@
         <v>64</v>
       </c>
       <c r="G19" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H19" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -1358,10 +1340,10 @@
         <v>80</v>
       </c>
       <c r="G20" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="H20" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -1384,10 +1366,10 @@
         <v>86</v>
       </c>
       <c r="G21" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="H21" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -1395,39 +1377,39 @@
         <v>89</v>
       </c>
       <c r="B22" t="s">
-        <v>102</v>
+        <v>5</v>
       </c>
       <c r="C22" t="s">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="D22" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E22" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F22" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G22" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="H22" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B23" t="s">
         <v>5</v>
       </c>
       <c r="C23" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D23" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E23" t="s">
         <v>15</v>
@@ -1436,36 +1418,10 @@
         <v>95</v>
       </c>
       <c r="G23" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="H23" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>96</v>
-      </c>
-      <c r="B24" t="s">
-        <v>5</v>
-      </c>
-      <c r="C24" t="s">
-        <v>97</v>
-      </c>
-      <c r="D24" t="s">
-        <v>99</v>
-      </c>
-      <c r="E24" t="s">
-        <v>15</v>
-      </c>
-      <c r="F24" t="s">
-        <v>98</v>
-      </c>
-      <c r="G24" t="s">
-        <v>145</v>
-      </c>
-      <c r="H24" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
